--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/109.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/109.xlsx
@@ -426,13 +426,13 @@
         <v>9.658173921157536</v>
       </c>
       <c r="E2">
-        <v>-17.84904124810242</v>
+        <v>-15.79043319200753</v>
       </c>
       <c r="F2">
-        <v>-4.071096241780763</v>
+        <v>-4.33450050852295</v>
       </c>
       <c r="G2">
-        <v>-9.1246691787593</v>
+        <v>-11.01668059192319</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>9.270382103672938</v>
       </c>
       <c r="E3">
-        <v>-18.33634127911981</v>
+        <v>-19.10571995607499</v>
       </c>
       <c r="F3">
-        <v>-3.973042392311386</v>
+        <v>-4.403443042355745</v>
       </c>
       <c r="G3">
-        <v>-10.10860908778999</v>
+        <v>-11.80581437696965</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>8.845761759316765</v>
       </c>
       <c r="E4">
-        <v>-18.98746338583868</v>
+        <v>-20.65649135152769</v>
       </c>
       <c r="F4">
-        <v>-4.104423119130193</v>
+        <v>-4.227628688050772</v>
       </c>
       <c r="G4">
-        <v>-9.773563554355086</v>
+        <v>-11.79036310464622</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>8.450338248269242</v>
       </c>
       <c r="E5">
-        <v>-18.2649000731748</v>
+        <v>-19.63775225334015</v>
       </c>
       <c r="F5">
-        <v>-4.023306897945857</v>
+        <v>-4.283566682027018</v>
       </c>
       <c r="G5">
-        <v>-10.09332843898765</v>
+        <v>-12.46250493499067</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>8.108170393317849</v>
       </c>
       <c r="E6">
-        <v>-19.61097538653279</v>
+        <v>-22.31167124370124</v>
       </c>
       <c r="F6">
-        <v>-4.151612724965473</v>
+        <v>-3.826309532416496</v>
       </c>
       <c r="G6">
-        <v>-9.29751080562461</v>
+        <v>-12.67560058794725</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>7.849766365403858</v>
       </c>
       <c r="E7">
-        <v>-20.1735024277656</v>
+        <v>-19.65748281459156</v>
       </c>
       <c r="F7">
-        <v>-3.933514356584599</v>
+        <v>-4.034274482358922</v>
       </c>
       <c r="G7">
-        <v>-9.075818352182287</v>
+        <v>-12.13410715643521</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>7.699664555381836</v>
       </c>
       <c r="E8">
-        <v>-20.37766867840142</v>
+        <v>-22.23391281651554</v>
       </c>
       <c r="F8">
-        <v>-4.024496433536277</v>
+        <v>-4.111264605509914</v>
       </c>
       <c r="G8">
-        <v>-9.441841898359904</v>
+        <v>-12.9655522934907</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>7.672727605335161</v>
       </c>
       <c r="E9">
-        <v>-20.93191766914821</v>
+        <v>-22.3853812151241</v>
       </c>
       <c r="F9">
-        <v>-3.983117825031636</v>
+        <v>-4.382558243396364</v>
       </c>
       <c r="G9">
-        <v>-9.376837618045744</v>
+        <v>-11.17810028654008</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>7.778084302142566</v>
       </c>
       <c r="E10">
-        <v>-21.1552529502585</v>
+        <v>-22.5503399378015</v>
       </c>
       <c r="F10">
-        <v>-3.881110177948697</v>
+        <v>-3.718693009649201</v>
       </c>
       <c r="G10">
-        <v>-8.97877622456171</v>
+        <v>-11.26702467202259</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>8.019886741048776</v>
       </c>
       <c r="E11">
-        <v>-22.32433285702669</v>
+        <v>-21.26058525567691</v>
       </c>
       <c r="F11">
-        <v>-3.722172981108362</v>
+        <v>-3.331125581268799</v>
       </c>
       <c r="G11">
-        <v>-9.558423700366975</v>
+        <v>-11.24002678103147</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>8.381454624796433</v>
       </c>
       <c r="E12">
-        <v>-22.25018815209911</v>
+        <v>-22.64529298079434</v>
       </c>
       <c r="F12">
-        <v>-3.841654210185954</v>
+        <v>-3.272418355064995</v>
       </c>
       <c r="G12">
-        <v>-8.119831169616509</v>
+        <v>-11.45348336835959</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>8.840860850375591</v>
       </c>
       <c r="E13">
-        <v>-22.92815958120946</v>
+        <v>-23.52394826402861</v>
       </c>
       <c r="F13">
-        <v>-3.472348141200267</v>
+        <v>-3.283660129088387</v>
       </c>
       <c r="G13">
-        <v>-9.047944375034804</v>
+        <v>-10.38809041533725</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>9.366786162454467</v>
       </c>
       <c r="E14">
-        <v>-23.71167162554258</v>
+        <v>-23.3805405491537</v>
       </c>
       <c r="F14">
-        <v>-3.071646947648479</v>
+        <v>-2.505661606216106</v>
       </c>
       <c r="G14">
-        <v>-9.355109368879102</v>
+        <v>-10.58857961506244</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>9.916812527202833</v>
       </c>
       <c r="E15">
-        <v>-25.05288788629034</v>
+        <v>-24.77070961392438</v>
       </c>
       <c r="F15">
-        <v>-2.802333107854721</v>
+        <v>-2.67028554527666</v>
       </c>
       <c r="G15">
-        <v>-8.803939614988257</v>
+        <v>-9.826410908791503</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>10.45499252922822</v>
       </c>
       <c r="E16">
-        <v>-25.61733047202839</v>
+        <v>-26.06395122103488</v>
       </c>
       <c r="F16">
-        <v>-2.243937268566796</v>
+        <v>-2.221111604782656</v>
       </c>
       <c r="G16">
-        <v>-8.209543048273288</v>
+        <v>-11.34260104820128</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>10.94012508892581</v>
       </c>
       <c r="E17">
-        <v>-26.37848996865965</v>
+        <v>-26.14982467364234</v>
       </c>
       <c r="F17">
-        <v>-2.246644373239145</v>
+        <v>-1.837012550717775</v>
       </c>
       <c r="G17">
-        <v>-8.493125902769856</v>
+        <v>-10.82271117943662</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>11.34491997972861</v>
       </c>
       <c r="E18">
-        <v>-26.4707395126699</v>
+        <v>-26.94547302831601</v>
       </c>
       <c r="F18">
-        <v>-2.021931491146917</v>
+        <v>-1.980021899137082</v>
       </c>
       <c r="G18">
-        <v>-8.209093520919643</v>
+        <v>-10.06313463819764</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>11.64999973175681</v>
       </c>
       <c r="E19">
-        <v>-27.4558592198245</v>
+        <v>-29.41580994118828</v>
       </c>
       <c r="F19">
-        <v>-1.401867840557584</v>
+        <v>-1.659828905095975</v>
       </c>
       <c r="G19">
-        <v>-8.56324560749519</v>
+        <v>-9.852755836692285</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>11.8369082144315</v>
       </c>
       <c r="E20">
-        <v>-29.34915986074339</v>
+        <v>-29.50952218230301</v>
       </c>
       <c r="F20">
-        <v>-1.087244788932901</v>
+        <v>-0.7170068066190646</v>
       </c>
       <c r="G20">
-        <v>-8.137241331210923</v>
+        <v>-10.6738027826259</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>11.89942272675041</v>
       </c>
       <c r="E21">
-        <v>-29.80753652827379</v>
+        <v>-30.40647250052827</v>
       </c>
       <c r="F21">
-        <v>-0.641168942525367</v>
+        <v>-0.7287132947554272</v>
       </c>
       <c r="G21">
-        <v>-8.717951922801449</v>
+        <v>-10.03495878866669</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>11.84033478781927</v>
       </c>
       <c r="E22">
-        <v>-29.32322529010146</v>
+        <v>-29.86874338296146</v>
       </c>
       <c r="F22">
-        <v>-0.3477926864150886</v>
+        <v>-0.1245750074849142</v>
       </c>
       <c r="G22">
-        <v>-8.461015868589129</v>
+        <v>-10.76699603735725</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>11.6676468970336</v>
       </c>
       <c r="E23">
-        <v>-30.03263338577306</v>
+        <v>-32.04685333964476</v>
       </c>
       <c r="F23">
-        <v>-0.3241237446148983</v>
+        <v>0.2645232438558612</v>
       </c>
       <c r="G23">
-        <v>-9.173254226389997</v>
+        <v>-10.29388326314403</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>11.40303291993524</v>
       </c>
       <c r="E24">
-        <v>-30.50772012239176</v>
+        <v>-30.80058785765283</v>
       </c>
       <c r="F24">
-        <v>0.2244484856432267</v>
+        <v>-0.713943503963512</v>
       </c>
       <c r="G24">
-        <v>-10.1866430989167</v>
+        <v>-10.08479398171154</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>11.06729323089182</v>
       </c>
       <c r="E25">
-        <v>-30.98307403897692</v>
+        <v>-29.97578518731777</v>
       </c>
       <c r="F25">
-        <v>0.2826934828362683</v>
+        <v>-0.4427708077178715</v>
       </c>
       <c r="G25">
-        <v>-8.603496352364898</v>
+        <v>-10.79297674966493</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>10.68803959873968</v>
       </c>
       <c r="E26">
-        <v>-30.81907308855214</v>
+        <v>-32.07094482136556</v>
       </c>
       <c r="F26">
-        <v>0.8968061420038902</v>
+        <v>0.2682310163507918</v>
       </c>
       <c r="G26">
-        <v>-9.1282128980435</v>
+        <v>-11.45388367738984</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>10.29827910887316</v>
       </c>
       <c r="E27">
-        <v>-29.9738560573905</v>
+        <v>-31.25412811494304</v>
       </c>
       <c r="F27">
-        <v>0.5404118357256393</v>
+        <v>0.7207117995167713</v>
       </c>
       <c r="G27">
-        <v>-8.341185657238208</v>
+        <v>-10.80260057249878</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>9.921922508622337</v>
       </c>
       <c r="E28">
-        <v>-30.92544920722932</v>
+        <v>-31.88452566036581</v>
       </c>
       <c r="F28">
-        <v>0.161601079160231</v>
+        <v>0.6493496045003995</v>
       </c>
       <c r="G28">
-        <v>-9.191586411242614</v>
+        <v>-11.04060069709154</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>9.582552006767076</v>
       </c>
       <c r="E29">
-        <v>-29.78051512387002</v>
+        <v>-30.65721863480699</v>
       </c>
       <c r="F29">
-        <v>0.5334841991360271</v>
+        <v>0.9081829399139386</v>
       </c>
       <c r="G29">
-        <v>-9.446041861955994</v>
+        <v>-9.97321276136106</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>9.30335730545184</v>
       </c>
       <c r="E30">
-        <v>-29.48553938395839</v>
+        <v>-29.28643143878914</v>
       </c>
       <c r="F30">
-        <v>0.07327971830634492</v>
+        <v>0.3093793387174544</v>
       </c>
       <c r="G30">
-        <v>-9.351207996444922</v>
+        <v>-11.24600844793434</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>9.096431121510459</v>
       </c>
       <c r="E31">
-        <v>-30.18411989827765</v>
+        <v>-29.74017547740969</v>
       </c>
       <c r="F31">
-        <v>0.3113442261968948</v>
+        <v>-0.1275745258504512</v>
       </c>
       <c r="G31">
-        <v>-8.279853063849067</v>
+        <v>-10.24442869180008</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>8.97724129822438</v>
       </c>
       <c r="E32">
-        <v>-28.99669514330438</v>
+        <v>-30.37267876324603</v>
       </c>
       <c r="F32">
-        <v>0.04825059723075785</v>
+        <v>-0.0692997074309088</v>
       </c>
       <c r="G32">
-        <v>-9.393460286465892</v>
+        <v>-10.43557625374553</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>8.947240384156975</v>
       </c>
       <c r="E33">
-        <v>-28.98323651855359</v>
+        <v>-29.61800177715675</v>
       </c>
       <c r="F33">
-        <v>0.5886219902011678</v>
+        <v>-0.2605871364527734</v>
       </c>
       <c r="G33">
-        <v>-8.562609050512657</v>
+        <v>-10.76259263802447</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>9.00580546811651</v>
       </c>
       <c r="E34">
-        <v>-28.50459040136485</v>
+        <v>-29.81918149918451</v>
       </c>
       <c r="F34">
-        <v>0.308125190469616</v>
+        <v>-0.5447411782676851</v>
       </c>
       <c r="G34">
-        <v>-8.185554037452187</v>
+        <v>-9.639781588933406</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>9.150656546586037</v>
       </c>
       <c r="E35">
-        <v>-28.13743531424496</v>
+        <v>-28.76853703737592</v>
       </c>
       <c r="F35">
-        <v>-0.0198643975666399</v>
+        <v>-0.04073677101497904</v>
       </c>
       <c r="G35">
-        <v>-7.826690116717278</v>
+        <v>-9.291348671535973</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>9.364652541034793</v>
       </c>
       <c r="E36">
-        <v>-27.96526273247333</v>
+        <v>-28.7289672314969</v>
       </c>
       <c r="F36">
-        <v>-0.3881582015861057</v>
+        <v>0.2698852660541824</v>
       </c>
       <c r="G36">
-        <v>-7.859482644982368</v>
+        <v>-9.934343410767877</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>9.63337082115757</v>
       </c>
       <c r="E37">
-        <v>-27.69101381809481</v>
+        <v>-28.26621605807509</v>
       </c>
       <c r="F37">
-        <v>-0.5503856737503608</v>
+        <v>-0.08403387842450361</v>
       </c>
       <c r="G37">
-        <v>-8.222343093576681</v>
+        <v>-9.965895637283499</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>9.939924743869229</v>
       </c>
       <c r="E38">
-        <v>-27.23779961093315</v>
+        <v>-27.31612409736982</v>
       </c>
       <c r="F38">
-        <v>-0.3508535039684327</v>
+        <v>-0.2937707062415188</v>
       </c>
       <c r="G38">
-        <v>-8.251759244857103</v>
+        <v>-8.484450352966684</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>10.26514754022297</v>
       </c>
       <c r="E39">
-        <v>-27.98049651903514</v>
+        <v>-27.57085076030128</v>
       </c>
       <c r="F39">
-        <v>-0.4039485410182699</v>
+        <v>-0.9338816763460032</v>
       </c>
       <c r="G39">
-        <v>-7.683130111048452</v>
+        <v>-8.726886689107817</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>10.5974989933288</v>
       </c>
       <c r="E40">
-        <v>-26.7639808470366</v>
+        <v>-27.85773864563521</v>
       </c>
       <c r="F40">
-        <v>-0.5027943097247237</v>
+        <v>-0.4055166405117693</v>
       </c>
       <c r="G40">
-        <v>-6.719346746057434</v>
+        <v>-7.717169503506132</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>10.91721008805019</v>
       </c>
       <c r="E41">
-        <v>-26.47101574958437</v>
+        <v>-25.69234464396545</v>
       </c>
       <c r="F41">
-        <v>-0.9067600992109446</v>
+        <v>-0.5218094834559863</v>
       </c>
       <c r="G41">
-        <v>-7.127222273225769</v>
+        <v>-9.09577474170683</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>11.21551815098328</v>
       </c>
       <c r="E42">
-        <v>-24.83781707024405</v>
+        <v>-25.26160978177787</v>
       </c>
       <c r="F42">
-        <v>-0.930126686909113</v>
+        <v>-1.200468530649746</v>
       </c>
       <c r="G42">
-        <v>-6.379349849289333</v>
+        <v>-9.454632099998619</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>11.4870998742145</v>
       </c>
       <c r="E43">
-        <v>-24.76940088493616</v>
+        <v>-23.52091418644347</v>
       </c>
       <c r="F43">
-        <v>-0.9610910604257585</v>
+        <v>-0.4737964804223242</v>
       </c>
       <c r="G43">
-        <v>-6.65011953359627</v>
+        <v>-10.45934542272215</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>11.72167885720728</v>
       </c>
       <c r="E44">
-        <v>-24.82542716535906</v>
+        <v>-24.4411091617501</v>
       </c>
       <c r="F44">
-        <v>-0.9171296023591888</v>
+        <v>-0.9105739027334335</v>
       </c>
       <c r="G44">
-        <v>-6.459352593351714</v>
+        <v>-9.408721247938869</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>11.91828192921494</v>
       </c>
       <c r="E45">
-        <v>-23.73017044186391</v>
+        <v>-25.96024010931121</v>
       </c>
       <c r="F45">
-        <v>-1.080278219075357</v>
+        <v>-0.8087277872940399</v>
       </c>
       <c r="G45">
-        <v>-6.838904616018922</v>
+        <v>-9.420015212546478</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>12.07376720319918</v>
       </c>
       <c r="E46">
-        <v>-23.65824016072607</v>
+        <v>-23.236661872982</v>
       </c>
       <c r="F46">
-        <v>-0.9329439644460341</v>
+        <v>-0.8898580907242235</v>
       </c>
       <c r="G46">
-        <v>-6.729905717035727</v>
+        <v>-9.138473277859884</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>12.18633638668145</v>
       </c>
       <c r="E47">
-        <v>-22.76676023910208</v>
+        <v>-22.01325386354378</v>
       </c>
       <c r="F47">
-        <v>-1.166568423057579</v>
+        <v>-0.853204489885151</v>
       </c>
       <c r="G47">
-        <v>-6.722467187760466</v>
+        <v>-8.288768142826079</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>12.26026359623679</v>
       </c>
       <c r="E48">
-        <v>-22.46255546916282</v>
+        <v>-22.25233012030473</v>
       </c>
       <c r="F48">
-        <v>-0.8446267454291621</v>
+        <v>-0.915116669570386</v>
       </c>
       <c r="G48">
-        <v>-6.438648085311617</v>
+        <v>-8.953996439344783</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>12.29221505789803</v>
       </c>
       <c r="E49">
-        <v>-21.65882831685946</v>
+        <v>-22.97826714610433</v>
       </c>
       <c r="F49">
-        <v>-1.21511075286163</v>
+        <v>-0.8489947267441239</v>
       </c>
       <c r="G49">
-        <v>-6.511366517512031</v>
+        <v>-7.979060202273212</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>12.28518080411475</v>
       </c>
       <c r="E50">
-        <v>-20.83226407013542</v>
+        <v>-20.45819853167982</v>
       </c>
       <c r="F50">
-        <v>-1.494590317422544</v>
+        <v>-0.1877471339898073</v>
       </c>
       <c r="G50">
-        <v>-7.039889280199588</v>
+        <v>-9.712040650115497</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>12.24587359066544</v>
       </c>
       <c r="E51">
-        <v>-19.98582435099171</v>
+        <v>-18.98558859759951</v>
       </c>
       <c r="F51">
-        <v>-1.009964737190929</v>
+        <v>-1.257430386735851</v>
       </c>
       <c r="G51">
-        <v>-6.298786016340286</v>
+        <v>-8.612381900347874</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>12.1719358980644</v>
       </c>
       <c r="E52">
-        <v>-19.64131163391017</v>
+        <v>-19.58097877470598</v>
       </c>
       <c r="F52">
-        <v>-1.283424555835699</v>
+        <v>-1.164960561928745</v>
       </c>
       <c r="G52">
-        <v>-6.077638245676831</v>
+        <v>-10.07269939904342</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>12.06443370363975</v>
       </c>
       <c r="E53">
-        <v>-19.40937225218531</v>
+        <v>-18.99819134076285</v>
       </c>
       <c r="F53">
-        <v>-0.8269775495451158</v>
+        <v>-0.9054338829990626</v>
       </c>
       <c r="G53">
-        <v>-6.898681910388885</v>
+        <v>-9.537148259775535</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>11.92317136676062</v>
       </c>
       <c r="E54">
-        <v>-19.94929315117184</v>
+        <v>-20.07619004981477</v>
       </c>
       <c r="F54">
-        <v>-0.9870255870726055</v>
+        <v>-1.207311673764272</v>
       </c>
       <c r="G54">
-        <v>-7.596243364154356</v>
+        <v>-10.22720884105611</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>11.74267698315459</v>
       </c>
       <c r="E55">
-        <v>-18.19805526834758</v>
+        <v>-21.35674287275578</v>
       </c>
       <c r="F55">
-        <v>-0.6141020376388933</v>
+        <v>-0.6849862646638497</v>
       </c>
       <c r="G55">
-        <v>-6.368069009567962</v>
+        <v>-8.054554547912916</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>11.52476241767817</v>
       </c>
       <c r="E56">
-        <v>-18.35111316133283</v>
+        <v>-16.13970080679712</v>
       </c>
       <c r="F56">
-        <v>-0.8160248757453007</v>
+        <v>-0.9826468369814073</v>
       </c>
       <c r="G56">
-        <v>-7.31955763737574</v>
+        <v>-10.58659775724054</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>11.26663675417292</v>
       </c>
       <c r="E57">
-        <v>-17.81417199824335</v>
+        <v>-18.40599826630579</v>
       </c>
       <c r="F57">
-        <v>-0.6427055640575602</v>
+        <v>-0.9858857535263533</v>
       </c>
       <c r="G57">
-        <v>-6.346659038892585</v>
+        <v>-9.287227457257309</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>10.96710811393603</v>
       </c>
       <c r="E58">
-        <v>-17.51707693249613</v>
+        <v>-18.20572197484256</v>
       </c>
       <c r="F58">
-        <v>-1.004670641119638</v>
+        <v>-1.189518341952139</v>
       </c>
       <c r="G58">
-        <v>-6.275308876082459</v>
+        <v>-9.055563371495834</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>10.63612949765647</v>
       </c>
       <c r="E59">
-        <v>-16.86390342705178</v>
+        <v>-19.08119826932345</v>
       </c>
       <c r="F59">
-        <v>-0.8392962011921472</v>
+        <v>-1.147174685423237</v>
       </c>
       <c r="G59">
-        <v>-7.109776018194202</v>
+        <v>-8.445866468649173</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>10.27589206990434</v>
       </c>
       <c r="E60">
-        <v>-16.61883147070468</v>
+        <v>-15.22091871538088</v>
       </c>
       <c r="F60">
-        <v>-0.6905495801410512</v>
+        <v>-0.6183888389483807</v>
       </c>
       <c r="G60">
-        <v>-6.407968663730809</v>
+        <v>-9.670949912526572</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>9.895244748938159</v>
       </c>
       <c r="E61">
-        <v>-16.310252194874</v>
+        <v>-14.79698109267882</v>
       </c>
       <c r="F61">
-        <v>-0.6206958421651773</v>
+        <v>-1.095322199477599</v>
       </c>
       <c r="G61">
-        <v>-7.717048098308433</v>
+        <v>-10.22655915918735</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>9.507826234804948</v>
       </c>
       <c r="E62">
-        <v>-16.6248679265569</v>
+        <v>-16.65806616950713</v>
       </c>
       <c r="F62">
-        <v>-0.748884869380998</v>
+        <v>-0.9460180871644187</v>
       </c>
       <c r="G62">
-        <v>-7.543389447274821</v>
+        <v>-9.044515498505184</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>9.123038920035672</v>
       </c>
       <c r="E63">
-        <v>-14.87214923273214</v>
+        <v>-15.98064721422572</v>
       </c>
       <c r="F63">
-        <v>-1.036563614494822</v>
+        <v>-1.31072423196236</v>
       </c>
       <c r="G63">
-        <v>-7.769783891211828</v>
+        <v>-9.601092705525994</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>8.759393915153499</v>
       </c>
       <c r="E64">
-        <v>-16.27493462608818</v>
+        <v>-15.10741251437863</v>
       </c>
       <c r="F64">
-        <v>-1.081477695074611</v>
+        <v>-1.261736240495603</v>
       </c>
       <c r="G64">
-        <v>-7.164014610571822</v>
+        <v>-10.78043263964317</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>8.428552670715325</v>
       </c>
       <c r="E65">
-        <v>-14.72700711231229</v>
+        <v>-15.76243816569211</v>
       </c>
       <c r="F65">
-        <v>-1.14027521332532</v>
+        <v>-1.267145479635883</v>
       </c>
       <c r="G65">
-        <v>-8.086700675530796</v>
+        <v>-9.144960252882905</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>8.141696859292271</v>
       </c>
       <c r="E66">
-        <v>-15.12775441962108</v>
+        <v>-16.32846571733285</v>
       </c>
       <c r="F66">
-        <v>-0.9968740471244888</v>
+        <v>-0.9106178062057819</v>
       </c>
       <c r="G66">
-        <v>-7.3163650087984</v>
+        <v>-8.425132429615042</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>7.916342298808691</v>
       </c>
       <c r="E67">
-        <v>-15.30080099687619</v>
+        <v>-14.4864862723429</v>
       </c>
       <c r="F67">
-        <v>-1.290402722836882</v>
+        <v>-0.7252134424785993</v>
       </c>
       <c r="G67">
-        <v>-8.153795093978321</v>
+        <v>-9.450455104953447</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>7.757639783470125</v>
       </c>
       <c r="E68">
-        <v>-15.0098057856173</v>
+        <v>-16.49345613932832</v>
       </c>
       <c r="F68">
-        <v>-1.224680881466172</v>
+        <v>-1.894144222121454</v>
       </c>
       <c r="G68">
-        <v>-7.983463601605987</v>
+        <v>-9.575459802703612</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>7.674678078686323</v>
       </c>
       <c r="E69">
-        <v>-15.58085088645854</v>
+        <v>-16.04847469791261</v>
       </c>
       <c r="F69">
-        <v>-1.107937406654832</v>
+        <v>-2.173272558903582</v>
       </c>
       <c r="G69">
-        <v>-7.69047020367693</v>
+        <v>-9.006440203529387</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>7.670141071507525</v>
       </c>
       <c r="E70">
-        <v>-14.59549569865554</v>
+        <v>-14.79229412208088</v>
       </c>
       <c r="F70">
-        <v>-1.641170757715319</v>
+        <v>-1.458680590511185</v>
       </c>
       <c r="G70">
-        <v>-7.936886661569669</v>
+        <v>-9.788292957935434</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>7.745216666242549</v>
       </c>
       <c r="E71">
-        <v>-15.13790725834628</v>
+        <v>-15.1549841338292</v>
       </c>
       <c r="F71">
-        <v>-1.640773141361975</v>
+        <v>-1.774520513850581</v>
       </c>
       <c r="G71">
-        <v>-7.863702295907814</v>
+        <v>-9.0256222247659</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>7.904196530822256</v>
       </c>
       <c r="E72">
-        <v>-14.07775526535859</v>
+        <v>-14.73221032894711</v>
       </c>
       <c r="F72">
-        <v>-2.014314652878176</v>
+        <v>-1.511513035094335</v>
       </c>
       <c r="G72">
-        <v>-7.315160800486084</v>
+        <v>-8.6855039228001</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>8.139850693548935</v>
       </c>
       <c r="E73">
-        <v>-14.56375562433578</v>
+        <v>-15.93406733058282</v>
       </c>
       <c r="F73">
-        <v>-1.866750112110875</v>
+        <v>-2.285895734253397</v>
       </c>
       <c r="G73">
-        <v>-7.859607331401627</v>
+        <v>-9.530182226404834</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>8.450535551462389</v>
       </c>
       <c r="E74">
-        <v>-14.34732626608719</v>
+        <v>-15.51749300661722</v>
       </c>
       <c r="F74">
-        <v>-2.101664338768578</v>
+        <v>-1.806592414584769</v>
       </c>
       <c r="G74">
-        <v>-8.008856975254529</v>
+        <v>-9.37993509119786</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>8.831889410294345</v>
       </c>
       <c r="E75">
-        <v>-14.46025735089047</v>
+        <v>-13.51396930835164</v>
       </c>
       <c r="F75">
-        <v>-2.411181333722405</v>
+        <v>-1.889647843859059</v>
       </c>
       <c r="G75">
-        <v>-7.489393665292599</v>
+        <v>-8.765762602144118</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>9.270364965237754</v>
       </c>
       <c r="E76">
-        <v>-15.10239496517813</v>
+        <v>-16.23286510255693</v>
       </c>
       <c r="F76">
-        <v>-1.877055002601701</v>
+        <v>-2.544229564123048</v>
       </c>
       <c r="G76">
-        <v>-6.983681954886301</v>
+        <v>-8.465547235562724</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>9.759287932666073</v>
       </c>
       <c r="E77">
-        <v>-16.46634416544439</v>
+        <v>-17.12406878726645</v>
       </c>
       <c r="F77">
-        <v>-2.45851756058798</v>
+        <v>-2.374371999811606</v>
       </c>
       <c r="G77">
-        <v>-6.928685400328447</v>
+        <v>-9.524315402256546</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>10.27861147166224</v>
       </c>
       <c r="E78">
-        <v>-16.24787699389235</v>
+        <v>-17.55964005969422</v>
       </c>
       <c r="F78">
-        <v>-2.132147430824197</v>
+        <v>-2.396442192524394</v>
       </c>
       <c r="G78">
-        <v>-6.626343802176534</v>
+        <v>-7.993658356991181</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>10.81706477525015</v>
       </c>
       <c r="E79">
-        <v>-16.36061335431331</v>
+        <v>-15.99594439942363</v>
       </c>
       <c r="F79">
-        <v>-2.767303935492538</v>
+        <v>-2.840146423057712</v>
       </c>
       <c r="G79">
-        <v>-6.703751099985394</v>
+        <v>-8.732051331842383</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>11.36265675724626</v>
       </c>
       <c r="E80">
-        <v>-17.05094298899059</v>
+        <v>-18.16225768131694</v>
       </c>
       <c r="F80">
-        <v>-2.828936955363029</v>
+        <v>-2.032940493930123</v>
       </c>
       <c r="G80">
-        <v>-6.456245276534919</v>
+        <v>-7.459288457484694</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>11.89297784710917</v>
       </c>
       <c r="E81">
-        <v>-17.91304217125282</v>
+        <v>-16.15627049319119</v>
       </c>
       <c r="F81">
-        <v>-2.789549742094719</v>
+        <v>-3.607259369889806</v>
       </c>
       <c r="G81">
-        <v>-5.477565165664022</v>
+        <v>-7.298958128425546</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>12.39479991101207</v>
       </c>
       <c r="E82">
-        <v>-17.40350733285777</v>
+        <v>-19.66108295142766</v>
       </c>
       <c r="F82">
-        <v>-2.690892841156103</v>
+        <v>-2.169122438215556</v>
       </c>
       <c r="G82">
-        <v>-5.643798412308611</v>
+        <v>-6.28871594737435</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>12.85219368472624</v>
       </c>
       <c r="E83">
-        <v>-18.4602584418657</v>
+        <v>-18.89315791462895</v>
       </c>
       <c r="F83">
-        <v>-2.954348466677263</v>
+        <v>-2.830592033433823</v>
       </c>
       <c r="G83">
-        <v>-4.776945613405148</v>
+        <v>-5.562214119454577</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>13.24559797828245</v>
       </c>
       <c r="E84">
-        <v>-18.89937550944148</v>
+        <v>-19.79431065673333</v>
       </c>
       <c r="F84">
-        <v>-3.361925109672287</v>
+        <v>-3.053002054146268</v>
       </c>
       <c r="G84">
-        <v>-4.650566083821576</v>
+        <v>-7.256184124176625</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>13.56465584493336</v>
       </c>
       <c r="E85">
-        <v>-19.71468196978245</v>
+        <v>-21.18120110632245</v>
       </c>
       <c r="F85">
-        <v>-3.4603442691663</v>
+        <v>-2.992846013354967</v>
       </c>
       <c r="G85">
-        <v>-4.748786169981994</v>
+        <v>-6.207072592532247</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>13.79214705958103</v>
       </c>
       <c r="E86">
-        <v>-20.70820199622128</v>
+        <v>-21.56048797530889</v>
       </c>
       <c r="F86">
-        <v>-3.542245782648489</v>
+        <v>-3.91260636333794</v>
       </c>
       <c r="G86">
-        <v>-4.199473587493795</v>
+        <v>-5.473650668343605</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>13.92115229701425</v>
       </c>
       <c r="E87">
-        <v>-22.04973072167557</v>
+        <v>-22.38149578442551</v>
       </c>
       <c r="F87">
-        <v>-3.659654436484277</v>
+        <v>-3.302745714048888</v>
       </c>
       <c r="G87">
-        <v>-4.059598393636226</v>
+        <v>-7.236719917885999</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>13.94987518966075</v>
       </c>
       <c r="E88">
-        <v>-23.17521500917192</v>
+        <v>-24.89230366950434</v>
       </c>
       <c r="F88">
-        <v>-4.139023197177726</v>
+        <v>-3.794482000066133</v>
       </c>
       <c r="G88">
-        <v>-3.318432786567294</v>
+        <v>-4.669036079979691</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>13.87320375617979</v>
       </c>
       <c r="E89">
-        <v>-24.93036549353881</v>
+        <v>-24.94212594053673</v>
       </c>
       <c r="F89">
-        <v>-3.982942211142243</v>
+        <v>-3.555804500297512</v>
       </c>
       <c r="G89">
-        <v>-4.291895755158674</v>
+        <v>-4.757428907569571</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>13.69136606870719</v>
       </c>
       <c r="E90">
-        <v>-26.74510163889862</v>
+        <v>-25.96421610948995</v>
       </c>
       <c r="F90">
-        <v>-4.600230002564795</v>
+        <v>-3.898763515669757</v>
       </c>
       <c r="G90">
-        <v>-4.147252946375232</v>
+        <v>-4.319375985719024</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>13.41406714797159</v>
       </c>
       <c r="E91">
-        <v>-26.96889882435769</v>
+        <v>-27.19995515365105</v>
       </c>
       <c r="F91">
-        <v>-4.974284273503329</v>
+        <v>-4.415126336204829</v>
       </c>
       <c r="G91">
-        <v>-3.487487883753005</v>
+        <v>-5.496940778972543</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>13.04344533629042</v>
       </c>
       <c r="E92">
-        <v>-28.86323648582433</v>
+        <v>-28.50131631465731</v>
       </c>
       <c r="F92">
-        <v>-4.779984072237482</v>
+        <v>-4.024186624127631</v>
       </c>
       <c r="G92">
-        <v>-4.411450343898601</v>
+        <v>-6.435557174602621</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>12.58781915421503</v>
       </c>
       <c r="E93">
-        <v>-30.48775860896595</v>
+        <v>-32.71824942449597</v>
       </c>
       <c r="F93">
-        <v>-5.118645517524005</v>
+        <v>-4.58714676780498</v>
       </c>
       <c r="G93">
-        <v>-3.649363668166651</v>
+        <v>-5.145085547488608</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>12.05596562453557</v>
       </c>
       <c r="E94">
-        <v>-32.25896932640104</v>
+        <v>-32.06497402838645</v>
       </c>
       <c r="F94">
-        <v>-5.226038381092543</v>
+        <v>-4.46181312302661</v>
       </c>
       <c r="G94">
-        <v>-3.789124019269639</v>
+        <v>-6.396494231937431</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>11.45447035277676</v>
       </c>
       <c r="E95">
-        <v>-34.15000573031609</v>
+        <v>-34.92592125950134</v>
       </c>
       <c r="F95">
-        <v>-5.599337180959724</v>
+        <v>-5.763488122233279</v>
       </c>
       <c r="G95">
-        <v>-5.057132403587692</v>
+        <v>-5.304280573888187</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>10.79280165775355</v>
       </c>
       <c r="E96">
-        <v>-36.02179385546154</v>
+        <v>-37.03584145457714</v>
       </c>
       <c r="F96">
-        <v>-6.045539767579886</v>
+        <v>-5.254095185025363</v>
       </c>
       <c r="G96">
-        <v>-3.827570092281653</v>
+        <v>-6.788111306278717</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>10.08756641202209</v>
       </c>
       <c r="E97">
-        <v>-37.99627192144192</v>
+        <v>-37.3247558320295</v>
       </c>
       <c r="F97">
-        <v>-5.944087126656822</v>
+        <v>-5.470000036523623</v>
       </c>
       <c r="G97">
-        <v>-4.994749819299529</v>
+        <v>-5.263360459820352</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>9.328306301835385</v>
       </c>
       <c r="E98">
-        <v>-38.89953719667088</v>
+        <v>-38.51039636824375</v>
       </c>
       <c r="F98">
-        <v>-6.20557123775932</v>
+        <v>-6.137379204793461</v>
       </c>
       <c r="G98">
-        <v>-6.074058432955477</v>
+        <v>-6.666085957704528</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>8.55937273525722</v>
       </c>
       <c r="E99">
-        <v>-41.02952532431166</v>
+        <v>-39.63804526631576</v>
       </c>
       <c r="F99">
-        <v>-6.606778563794219</v>
+        <v>-5.899100149745586</v>
       </c>
       <c r="G99">
-        <v>-5.945608452567895</v>
+        <v>-7.419628332495685</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>7.751149041787672</v>
       </c>
       <c r="E100">
-        <v>-43.79418587683846</v>
+        <v>-43.06575139762364</v>
       </c>
       <c r="F100">
-        <v>-6.521603756519866</v>
+        <v>-5.80655328677002</v>
       </c>
       <c r="G100">
-        <v>-6.541826097248356</v>
+        <v>-9.607766710177904</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>6.979038314651779</v>
       </c>
       <c r="E101">
-        <v>-45.25343454835915</v>
+        <v>-45.51791554430313</v>
       </c>
       <c r="F101">
-        <v>-6.397963708896519</v>
+        <v>-5.641295646646324</v>
       </c>
       <c r="G101">
-        <v>-7.150728944477631</v>
+        <v>-9.477347996854656</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>6.160743563505977</v>
       </c>
       <c r="E102">
-        <v>-47.90326205699944</v>
+        <v>-48.21006617101911</v>
       </c>
       <c r="F102">
-        <v>-6.627904417667814</v>
+        <v>-6.221112238603241</v>
       </c>
       <c r="G102">
-        <v>-7.844585899102489</v>
+        <v>-8.152357918935284</v>
       </c>
     </row>
   </sheetData>
